--- a/outputs/daily/hr_rankings_2026-07-01_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-01_full.xlsx
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>75</v>
       </c>
       <c r="U41" t="n">
-        <v>34.9</v>
+        <v>33.7</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>80</v>
       </c>
       <c r="U48" t="n">
-        <v>44.1</v>
+        <v>42.3</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
@@ -22991,27 +22991,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01T17:10:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -23021,26 +23021,26 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -23054,54 +23054,58 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>48.6</v>
+        <v>32.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>38.6</v>
+        <v>35.8</v>
       </c>
       <c r="R82" t="n">
-        <v>47.6</v>
+        <v>78.7</v>
       </c>
       <c r="S82" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T82" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U82" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23121,142 +23125,142 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Hot streak: 5 HR in last 7 games</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>101.8811</t>
+          <t>98.6226</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.4343</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3437</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>32.41</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.1898</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.3808</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -23267,47 +23271,47 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-02T00:10:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Troy Melton</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>675512</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -23330,58 +23334,62 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>32.7</v>
+        <v>44.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>35.8</v>
+        <v>50.8</v>
       </c>
       <c r="R83" t="n">
-        <v>78.7</v>
+        <v>40.1</v>
       </c>
       <c r="S83" t="n">
-        <v>96.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T83" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23401,142 +23409,142 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 8/30, 1 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>98.6226</t>
+          <t>101.8076</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.4063</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1771</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.1898</t>
+          <t>0.2166</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.3808</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23547,56 +23555,56 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-02T00:10:00Z</t>
+          <t>2026-07-01T17:10:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -23610,60 +23618,52 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>44.2</v>
+        <v>48.6</v>
       </c>
       <c r="Q84" t="n">
-        <v>50.8</v>
+        <v>38.6</v>
       </c>
       <c r="R84" t="n">
-        <v>40.1</v>
+        <v>47.6</v>
       </c>
       <c r="S84" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T84" t="n">
         <v>50</v>
       </c>
       <c r="U84" t="n">
-        <v>40.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -23690,22 +23690,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 1 HR</t>
+          <t>Hot streak: 5 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23715,112 +23715,112 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>101.8076</t>
+          <t>101.8811</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.4063</t>
+          <t>0.4343</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.1771</t>
+          <t>0.188</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.3437</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.2166</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -26636,7 +26636,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>29.7</v>
+        <v>27.7</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
@@ -29091,47 +29091,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-01T23:15:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -29154,26 +29154,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>49</v>
+        <v>39.3</v>
       </c>
       <c r="Q104" t="n">
-        <v>51.1</v>
+        <v>41.4</v>
       </c>
       <c r="R104" t="n">
-        <v>47.9</v>
+        <v>78.8</v>
       </c>
       <c r="S104" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T104" t="n">
         <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>6</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29225,27 +29225,27 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29255,112 +29255,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>44.02</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>102.393</t>
+          <t>100.0782</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.3965</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1851</t>
+          <t>0.1722</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3034</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>75.69</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1863</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4892</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29371,47 +29371,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-01T23:15:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29420,7 +29420,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29434,26 +29434,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Good Environment, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>39.3</v>
+        <v>49</v>
       </c>
       <c r="Q105" t="n">
-        <v>41.4</v>
+        <v>51.1</v>
       </c>
       <c r="R105" t="n">
-        <v>78.8</v>
+        <v>47.9</v>
       </c>
       <c r="S105" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>50</v>
       </c>
       <c r="U105" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
@@ -29515,17 +29515,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29535,112 +29535,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>100.0782</t>
+          <t>102.393</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.3965</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.1722</t>
+          <t>0.1851</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3034</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>75.69</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>58.26</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.1863</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.4892</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -31887,27 +31887,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31917,17 +31917,17 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Brad Lord</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>695418</t>
+          <t>607067</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -31950,26 +31950,26 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>21.7</v>
+        <v>17.9</v>
       </c>
       <c r="Q114" t="n">
-        <v>31.7</v>
+        <v>55.5</v>
       </c>
       <c r="R114" t="n">
-        <v>69.2</v>
+        <v>78.8</v>
       </c>
       <c r="S114" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T114" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>57.5</v>
+        <v>10.1</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -32021,27 +32021,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32051,112 +32051,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>90.28</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>98.1914</t>
+          <t>97.9991</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.3754</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3198</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1448</t>
+          <t>0.0736</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.4639</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>26.12</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32723,22 +32723,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>681546</t>
+          <t>678011</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>James Outman</t>
+          <t>Anthony Seigler</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32753,17 +32753,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Brad Lord</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>695418</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32786,26 +32786,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26.4</v>
+        <v>21.7</v>
       </c>
       <c r="Q117" t="n">
-        <v>42.9</v>
+        <v>31.7</v>
       </c>
       <c r="R117" t="n">
-        <v>78.7</v>
+        <v>69.2</v>
       </c>
       <c r="S117" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T117" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U117" t="n">
-        <v>47.2</v>
+        <v>54.9</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32857,27 +32857,27 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 12.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32887,102 +32887,102 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.44</t>
+          <t>90.28</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.2712</t>
+          <t>98.1914</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3754</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.2405</t>
+          <t>0.3198</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1448</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.4064</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH117" t="inlineStr">
@@ -32992,7 +32992,7 @@
       </c>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33003,47 +33003,47 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>681546</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>James Outman</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-01T16:35:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -33052,7 +33052,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -33070,22 +33070,22 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>9.699999999999999</v>
+        <v>26.4</v>
       </c>
       <c r="Q118" t="n">
-        <v>63.1</v>
+        <v>42.9</v>
       </c>
       <c r="R118" t="n">
-        <v>73.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="S118" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T118" t="n">
         <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>40.7</v>
+        <v>47.2</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -33137,127 +33137,127 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.8% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>32.58</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>87.44</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>97.7683</t>
+          <t>98.2712</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3124</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.0896</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2565</t>
+          <t>0.2405</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>16.94</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>40.33</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.4711</t>
+          <t>0.4064</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.2415</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG118" t="inlineStr">
@@ -33267,12 +33267,12 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -33283,47 +33283,47 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>660710</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rodolfo Durán</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-01T16:35:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>607067</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -33346,26 +33346,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>32.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q119" t="n">
-        <v>55.5</v>
+        <v>63.1</v>
       </c>
       <c r="R119" t="n">
-        <v>78.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S119" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T119" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -33400,7 +33400,7 @@
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -33417,142 +33417,142 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 7/26, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.8% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>32.58</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.66</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>97.8572</t>
+          <t>97.7683</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.3124</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>0.0896</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.2565</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>16.94</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>0.4639</t>
+          <t>0.4711</t>
         </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.2415</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -33563,52 +33563,52 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>677870</t>
+          <t>660710</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Leo Jimenez</t>
+          <t>Rodolfo Durán</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-02T00:40:00Z</t>
+          <t>2026-07-01T18:20:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Colin Rea</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>607067</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -33626,65 +33626,61 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>29.1</v>
+        <v>32.3</v>
       </c>
       <c r="Q120" t="n">
-        <v>62.5</v>
+        <v>55.5</v>
       </c>
       <c r="R120" t="n">
-        <v>38.7</v>
+        <v>78.8</v>
       </c>
       <c r="S120" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T120" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U120" t="n">
-        <v>34.9</v>
+        <v>0</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -33701,12 +33697,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33716,12 +33712,12 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Contact streak: 6/17 over last 7 games</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 17.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -33731,104 +33727,112 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>91.58</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>100.7363</t>
+          <t>97.8572</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.1031</t>
+          <t>0.171</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.2939</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.0631</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4968</t>
+          <t>0.4639</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.2029</t>
+          <t>0.1959</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>29.64</t>
-        </is>
-      </c>
-      <c r="BG120" t="inlineStr"/>
-      <c r="BH120" t="inlineStr"/>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -33839,27 +33843,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>677870</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Leo Jimenez</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-02T01:40:00Z</t>
+          <t>2026-07-02T00:40:00Z</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -33869,22 +33873,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -33902,26 +33906,26 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>50.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q121" t="n">
-        <v>59.3</v>
+        <v>62.5</v>
       </c>
       <c r="R121" t="n">
-        <v>28.2</v>
+        <v>38.7</v>
       </c>
       <c r="S121" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T121" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U121" t="n">
-        <v>25.3</v>
+        <v>34.9</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -33935,7 +33939,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -33977,27 +33981,27 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/17 over last 7 games</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 17.8 HR allowed</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -34007,104 +34011,104 @@
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>48.66</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>91.58</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>103.0202</t>
+          <t>100.7363</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>0.4471</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>0.1834</t>
+          <t>0.1031</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.2939</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.0631</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>45.13</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.4968</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.2029</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr"/>
@@ -34115,47 +34119,47 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-01T18:20:00Z</t>
+          <t>2026-07-02T01:40:00Z</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Colin Rea</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>607067</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -34164,7 +34168,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -34178,58 +34182,62 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>17.9</v>
+        <v>50.5</v>
       </c>
       <c r="Q122" t="n">
-        <v>55.5</v>
+        <v>59.3</v>
       </c>
       <c r="R122" t="n">
-        <v>78.8</v>
+        <v>28.2</v>
       </c>
       <c r="S122" t="n">
-        <v>64.3</v>
+        <v>47.9</v>
       </c>
       <c r="T122" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U122" t="n">
-        <v>2</v>
+        <v>25.3</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -34249,27 +34257,27 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 14.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -34279,112 +34287,104 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>48.66</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>97.9991</t>
+          <t>103.0202</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.4471</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1834</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3284</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>28.74</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>0.0736</t>
+          <t>0.1594</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>0.4639</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
-          <t>0.1959</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
         <is>
-          <t>26.12</t>
-        </is>
-      </c>
-      <c r="BG122" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH122" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ122" t="inlineStr"/>
@@ -50290,7 +50290,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -57647,32 +57647,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>606992</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Eric Haase</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-01T17:35:00Z</t>
+          <t>2026-07-02T01:40:00Z</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -57682,12 +57682,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Brad Lord</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>695418</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -57710,58 +57710,62 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P207" t="n">
-        <v>20.1</v>
+        <v>30.5</v>
       </c>
       <c r="Q207" t="n">
-        <v>32.7</v>
+        <v>59.3</v>
       </c>
       <c r="R207" t="n">
-        <v>69.2</v>
+        <v>28.2</v>
       </c>
       <c r="S207" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T207" t="n">
         <v>50</v>
       </c>
       <c r="U207" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W207" t="inlineStr">
+      <c r="Z207" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC207" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57781,27 +57785,27 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Contact streak: 6/15 over last 7 games</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -57811,112 +57815,104 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>84.89</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>99.6376</t>
+          <t>96.5647</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.3545</t>
+          <t>0.3694</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.3101</t>
+          <t>0.2744</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>72.37</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>13.95</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1973</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.4027</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="BG207" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH207" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>28.69</t>
+        </is>
+      </c>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -57927,27 +57923,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>606992</t>
+          <t>678662</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Eric Haase</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-07-02T01:40:00Z</t>
+          <t>2026-07-02T00:40:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -57957,17 +57953,17 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Max Meyer</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>668678</t>
+          <t>676974</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -57976,40 +57972,40 @@
         </is>
       </c>
       <c r="L208" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Projected Lineup</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="R208" t="n">
         <v>38.7</v>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Strong Barrel</t>
-        </is>
-      </c>
-      <c r="P208" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="R208" t="n">
-        <v>28.2</v>
-      </c>
       <c r="S208" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T208" t="n">
         <v>50</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58023,7 +58019,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -58065,27 +58061,27 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -58095,104 +58091,104 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>84.89</t>
+          <t>88.21</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>96.5647</t>
+          <t>99.1247</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.3694</t>
+          <t>0.3885</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2744</t>
+          <t>0.2889</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>71.81</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.1973</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.3914</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58203,47 +58199,47 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>678662</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-07-02T00:40:00Z</t>
+          <t>2026-07-01T17:35:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Max Meyer</t>
+          <t>Brad Lord</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>676974</t>
+          <t>695418</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -58252,7 +58248,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -58266,62 +58262,58 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>30.6</v>
+        <v>20.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>42.7</v>
+        <v>32.7</v>
       </c>
       <c r="R209" t="n">
-        <v>38.7</v>
+        <v>69.2</v>
       </c>
       <c r="S209" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T209" t="n">
         <v>50</v>
       </c>
       <c r="U209" t="n">
-        <v>25.3</v>
+        <v>56.6</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58341,12 +58333,12 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
@@ -58356,12 +58348,12 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 9.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58371,104 +58363,112 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.1247</t>
+          <t>99.6376</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3885</t>
+          <t>0.3545</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2889</t>
+          <t>0.3101</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>71.81</t>
+          <t>72.37</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>39.19</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.3914</t>
+          <t>0.4027</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1581</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>26.35</t>
-        </is>
-      </c>
-      <c r="BG209" t="inlineStr"/>
-      <c r="BH209" t="inlineStr"/>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH209" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -62099,47 +62099,47 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>669701</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Josh Smith</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-07-01T17:10:00Z</t>
+          <t>2026-07-01T23:40:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -62162,39 +62162,47 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>16.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q223" t="n">
-        <v>38.6</v>
+        <v>45.7</v>
       </c>
       <c r="R223" t="n">
-        <v>47.6</v>
+        <v>23.2</v>
       </c>
       <c r="S223" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T223" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U223" t="n">
-        <v>37.3</v>
+        <v>19.5</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W223" t="inlineStr"/>
-      <c r="X223" t="inlineStr"/>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z223" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -62202,17 +62210,17 @@
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -62229,12 +62237,12 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
@@ -62244,127 +62252,119 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Contact streak: 7/19 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>32.08</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>87.13</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>97.8652</t>
+          <t>100.2407</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.3352</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.0962</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>42.78</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.0555</t>
+          <t>0.1123</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="BG223" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH223" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -62375,47 +62375,47 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>669701</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Josh Smith</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-07-01T23:40:00Z</t>
+          <t>2026-07-01T17:10:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -62424,7 +62424,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -62438,65 +62438,57 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>23.7</v>
+        <v>16.5</v>
       </c>
       <c r="Q224" t="n">
-        <v>45.7</v>
+        <v>38.6</v>
       </c>
       <c r="R224" t="n">
-        <v>23.2</v>
+        <v>47.6</v>
       </c>
       <c r="S224" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T224" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>19.5</v>
+        <v>34.5</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr"/>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
+      <c r="Z224" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -62513,7 +62505,7 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
@@ -62528,119 +62520,127 @@
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>32.08</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>87.13</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>100.2407</t>
+          <t>97.8652</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.3352</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.0962</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>42.78</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.1123</t>
+          <t>0.0555</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>38.16</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.3854</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="BG224" t="inlineStr"/>
-      <c r="BH224" t="inlineStr"/>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -72710,7 +72710,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -72743,7 +72743,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -72800,7 +72800,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -72810,7 +72810,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
